--- a/산출물/06_테스트/하모니_테스트_산출물.xlsx
+++ b/산출물/06_테스트/하모니_테스트_산출물.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-1. 단위 결함" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. 통합 계획" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. 통합 결과" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-1. 실기기 증빙·미검증" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-1. 실기기 증빙" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. 단위 계획'!$A$5:$H$63</definedName>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +142,17 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FF191F28"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF4E5968"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="FF12805A"/>
       <sz val="10"/>
     </font>
@@ -205,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -288,14 +299,44 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -662,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -845,7 +886,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>통합 실행 결과 + 실기기 증빙·잔여 미검증</t>
+          <t>통합 실행 결과 (34/34)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -854,10 +895,27 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>※ 실기기 IT-RT(소리·카메라·제스처·2기기 합주)는 S23 Ultra 사람 육안 검증 성공. 증빙(스크린샷) 보유 — 학교 보관, 발표 전 테스트증빙_목록에 첨부. 상세: 앱인토스_실기기검수표.</t>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>4-1. 실기기 증빙</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>S23 Ultra 증빙 스크린샷 목록(EV-201~209)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>9건 보유</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>※ 실기기 IT-RT(소리·카메라·제스처·2기기 합주) 9건 S23 Ultra 사람 검증 성공. 증빙 스크린샷 EV-201~209 보유(학교 보관)·발표 전 첨부. 상세: 평가증빙/테스트증빙_목록.</t>
         </is>
       </c>
     </row>
@@ -9252,53 +9310,367 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>실기기 증빙 · 잔여 미검증</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>실기기 IT-RT(소리·카메라·제스처·2기기 합주) = S23 Ultra 사람 육안 검증 성공.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>실기기 증빙 (S23 Ultra) — 스크린샷 목록</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>토스 샌드박스 S23 Ultra 사람 육안 검증 9건 · 증빙 ID EV-201~209 · 사진 원본 보유(학교 보관), 평가증빙/실기기_스크린샷/에 첨부 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>증빙(스크린샷) 보유 — 학교 보관, 테스트증빙_목록에 파일 추후 첨부.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>제스처 스파이크 근거: commit 923e545(2026-06-21, S23 Ultra).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>잔여 미검증(기본 흐름·UX): RT-01 온보딩·RT-07 메트로놈·RT-09 로컬저장·RT-13 뒤로가기·RT-14 핀치줌·RT-15 느린네트워크.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>상세: 앱인토스_실기기검수표(RT-01~15).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+          <t>증빙 ID</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>증빙 파일 (평가증빙/)</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>실행자</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t>EV-201</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>RT-02</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>터치 코드 소리(Tone.js)</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-02_코드소리.jpg</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>EV-202</t>
+        </is>
+      </c>
+      <c r="B6" s="35" t="inlineStr">
+        <is>
+          <t>RT-03</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>AudioContext unlock</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-03_unlock.jpg</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="19" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>EV-203</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>RT-04</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>카메라 권한·손 인식</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-04_손인식.jpg</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="19" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>EV-204</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>RT-05</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>제스처 연주</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-05_제스처연주.jpg</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F8" s="38" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="19" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>EV-205</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>RT-06</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>카메라 거부 폴백</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-06_카메라폴백.jpg</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="19" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>EV-206</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>RT-08</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>녹음→재생</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-08_녹음재생.jpg</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>EV-207</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>RT-10</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>2기기 합주(공유→받기)</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-10_2기기합주.jpg</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
+        <is>
+          <t>EV-208</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>RT-11</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>합주 합쳐듣기 소리</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-11_합주소리.jpg</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>EV-209</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>RT-12</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>얹기→polling</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>실기기_스크린샷/RT-12_polling.jpg</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>양록빈</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>상세 매핑·환경: 평가증빙/테스트증빙_목록.md (EV-2xx). 제스처 근거 commit 923e545(2026-06-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>기본 UX 흐름(RT-01·07·09·13·14·15)은 앱인토스_실기기검수표에서 별도 점검.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
         <is>
           <t>결함: 없음 (전 시나리오 성공)</t>
         </is>
